--- a/email_marketing_forms/037_newsletter_release_form--email_marketing_forms.xlsx
+++ b/email_marketing_forms/037_newsletter_release_form--email_marketing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -750,8 +750,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -779,12 +779,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'issue_date',_'label':_'date'}</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'issue_date', 'label': 'Date'}</t>
+          <t>Date</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'issue_time',_'label':_'time'}</t>
+          <t>time</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'issue_time', 'label': 'Time'}</t>
+          <t>Time</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'issue_frequency',_'label':_'frequency'}</t>
+          <t>frequency</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'issue_frequency', 'label': 'Frequency'}</t>
+          <t>Frequency</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'email',_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'email', 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'social_media',_'label':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'social_media', 'label': 'Social Media'}</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'web_site',_'label':_'website'}</t>
+          <t>website</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'web_site', 'label': 'Website'}</t>
+          <t>Website</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'blog',_'label':_'blog'}</t>
+          <t>blog</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'blog', 'label': 'Blog'}</t>
+          <t>Blog</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'marketing_manager',_'label':_'marketing_manager'}</t>
+          <t>marketing_manager</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'marketing_manager', 'label': 'Marketing Manager'}</t>
+          <t>Marketing Manager</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'communications_officer',_'label':_'communications_officer'}</t>
+          <t>communications_officer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'communications_officer', 'label': 'Communications Officer'}</t>
+          <t>Communications Officer</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'creative_director',_'label':_'creative_director'}</t>
+          <t>creative_director</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'creative_director', 'label': 'Creative Director'}</t>
+          <t>Creative Director</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'editor',_'label':_'editor'}</t>
+          <t>editor</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'editor', 'label': 'Editor'}</t>
+          <t>Editor</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'publisher',_'label':_'publisher'}</t>
+          <t>publisher</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'publisher', 'label': 'Publisher'}</t>
+          <t>Publisher</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
